--- a/data/file_generation/input/data_136/员工工时分配表.xlsx
+++ b/data/file_generation/input/data_136/员工工时分配表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/田姣姣/input/data_136/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0BAD98-F0D7-954D-BBE6-A87421E78FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEBBE39-8277-BA47-AF6F-16E0648F975F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26160" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37220" yWindow="2180" windowWidth="26160" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工时统计" sheetId="3" r:id="rId1"/>
@@ -18,8 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工时统计!$A$1:$S$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,6 +44,57 @@
     <t>项目</t>
   </si>
   <si>
+    <t>王A</t>
+  </si>
+  <si>
+    <t>贾A</t>
+  </si>
+  <si>
+    <t>常A</t>
+  </si>
+  <si>
+    <t>黄A</t>
+  </si>
+  <si>
+    <t>代A</t>
+  </si>
+  <si>
+    <t>姜A</t>
+  </si>
+  <si>
+    <t>周A</t>
+  </si>
+  <si>
+    <t>王B</t>
+  </si>
+  <si>
+    <t>张A</t>
+  </si>
+  <si>
+    <t>赵A</t>
+  </si>
+  <si>
+    <t>田A</t>
+  </si>
+  <si>
+    <t>陈A</t>
+  </si>
+  <si>
+    <t>于A</t>
+  </si>
+  <si>
+    <t>只A</t>
+  </si>
+  <si>
+    <t>薛A</t>
+  </si>
+  <si>
+    <t>李A</t>
+  </si>
+  <si>
+    <t>蔡A</t>
+  </si>
+  <si>
     <t>总工时</t>
   </si>
   <si>
@@ -50,6 +104,10 @@
     <t>工时占比</t>
   </si>
   <si>
+    <t>-</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>物流园区能耗与碳排数据管理系统方案咨询报告</t>
   </si>
   <si>
@@ -62,8 +120,9 @@
     <t>物流园区能耗与碳排数智平台示范项目</t>
   </si>
   <si>
-    <t>新海轮渡智慧配电安全集中监测
+    <t>AA轮渡智慧配电安全集中监测
 系统项目</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>县电力公司配电监测（30套）</t>
@@ -123,61 +182,7 @@
     <t>水泥制品项目</t>
   </si>
   <si>
-    <t>滨海远宾仓储</t>
-  </si>
-  <si>
-    <t>王A</t>
-  </si>
-  <si>
-    <t>贾A</t>
-  </si>
-  <si>
-    <t>常A</t>
-  </si>
-  <si>
-    <t>黄A</t>
-  </si>
-  <si>
-    <t>代A</t>
-  </si>
-  <si>
-    <t>姜A</t>
-  </si>
-  <si>
-    <t>周A</t>
-  </si>
-  <si>
-    <t>王B</t>
-  </si>
-  <si>
-    <t>张A</t>
-  </si>
-  <si>
-    <t>赵A</t>
-  </si>
-  <si>
-    <t>田A</t>
-  </si>
-  <si>
-    <t>陈A</t>
-  </si>
-  <si>
-    <t>于A</t>
-  </si>
-  <si>
-    <t>只A</t>
-  </si>
-  <si>
-    <t>薛A</t>
-  </si>
-  <si>
-    <t>李A</t>
-  </si>
-  <si>
-    <t>蔡A</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>BB远宾仓储</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -332,9 +337,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -356,10 +358,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -633,73 +638,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16">
+    <row r="1" spans="1:19" ht="15.95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>45</v>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="60">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -722,7 +727,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -741,13 +746,13 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="S3" s="11" t="s">
-        <v>46</v>
+      <c r="S3" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="75">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -770,7 +775,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -789,13 +794,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="11" t="s">
-        <v>46</v>
+      <c r="S5" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="60">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -818,7 +823,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -837,13 +842,13 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="11" t="s">
-        <v>46</v>
+      <c r="S7" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="75">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -866,7 +871,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -885,13 +890,13 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="11" t="s">
-        <v>46</v>
+      <c r="S9" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="60">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -914,7 +919,7 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -933,13 +938,13 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="64">
-      <c r="A12" s="4" t="s">
-        <v>8</v>
+      <c r="S11" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="63.95">
+      <c r="A12" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -962,7 +967,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -981,13 +986,13 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="11" t="s">
-        <v>46</v>
+      <c r="S13" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="45">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1010,7 +1015,7 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1029,13 +1034,13 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="11" t="s">
-        <v>46</v>
+      <c r="S15" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="75">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1058,7 +1063,7 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1077,13 +1082,13 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="11" t="s">
-        <v>46</v>
+      <c r="S17" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="45">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1106,7 +1111,7 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1125,13 +1130,13 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="11" t="s">
-        <v>46</v>
+      <c r="S19" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="45">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1154,7 +1159,7 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1173,13 +1178,13 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-      <c r="S21" s="11" t="s">
-        <v>46</v>
+      <c r="S21" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="30">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1202,7 +1207,7 @@
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1221,13 +1226,13 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
-      <c r="S23" s="11" t="s">
-        <v>46</v>
+      <c r="S23" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="75">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1250,7 +1255,7 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1269,13 +1274,13 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="11" t="s">
-        <v>46</v>
+      <c r="S25" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="30">
-      <c r="A26" s="5" t="s">
-        <v>15</v>
+      <c r="A26" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1298,7 +1303,7 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1317,13 +1322,13 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="11" t="s">
-        <v>46</v>
+      <c r="S27" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="90">
-      <c r="A28" s="5" t="s">
-        <v>16</v>
+      <c r="A28" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1346,7 +1351,7 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1365,13 +1370,13 @@
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-      <c r="S29" s="11" t="s">
-        <v>46</v>
+      <c r="S29" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="60">
-      <c r="A30" s="5" t="s">
-        <v>17</v>
+      <c r="A30" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1413,13 +1418,13 @@
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="11" t="s">
-        <v>46</v>
+      <c r="S31" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="45">
-      <c r="A32" s="5" t="s">
-        <v>18</v>
+      <c r="A32" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1442,7 +1447,7 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1461,13 +1466,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="11" t="s">
-        <v>46</v>
+      <c r="S33" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="60">
-      <c r="A34" s="5" t="s">
-        <v>19</v>
+      <c r="A34" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1490,7 +1495,7 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1509,13 +1514,13 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
-      <c r="S35" s="11" t="s">
-        <v>46</v>
+      <c r="S35" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="45">
-      <c r="A36" s="5" t="s">
-        <v>20</v>
+      <c r="A36" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1538,7 +1543,7 @@
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1557,13 +1562,13 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
-      <c r="S37" s="11" t="s">
-        <v>46</v>
+      <c r="S37" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1586,7 +1591,7 @@
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1605,13 +1610,13 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="11" t="s">
-        <v>46</v>
+      <c r="S39" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="90">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1634,7 +1639,7 @@
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1653,13 +1658,13 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="11" t="s">
-        <v>46</v>
+      <c r="S41" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="90">
       <c r="A42" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1682,7 +1687,7 @@
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1701,13 +1706,13 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="11" t="s">
-        <v>46</v>
+      <c r="S43" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="75">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1730,7 +1735,7 @@
     </row>
     <row r="45" spans="1:19">
       <c r="A45" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1749,13 +1754,13 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="11" t="s">
-        <v>46</v>
+      <c r="S45" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="45">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1778,7 +1783,7 @@
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1797,13 +1802,13 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
-      <c r="S47" s="11" t="s">
-        <v>46</v>
+      <c r="S47" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="30">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="49" spans="1:19">
       <c r="A49" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1845,36 +1850,36 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="11" t="s">
-        <v>46</v>
+      <c r="S49" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="30">
-      <c r="A50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
+      <c r="A50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
       <c r="S50" s="2"/>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1893,36 +1898,36 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
-      <c r="S51" s="11" t="s">
+      <c r="S51" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
+      <c r="A52" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" ht="30">
-      <c r="A52" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
       <c r="S52" s="2"/>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1941,8 +1946,8 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
-      <c r="S53" s="11" t="s">
-        <v>46</v>
+      <c r="S53" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1953,8 +1958,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e51449f75ee7148e2b7755d0e75cc1e3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce7ff00e6adaab951c7f230000ea38d3" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1974,7 +1979,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="共享对象:" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1993,7 +1998,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="共享对象详细信息" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -2010,8 +2015,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2101,6 +2106,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2109,20 +2120,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FB1472D-7DA5-407D-8407-AD52B349F676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A890EE89-F197-4D02-AC36-E80A1DD4C91D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{055BEB3A-636B-4B7D-A5E1-A601C4AA710C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176DE07F-5C66-449F-A440-1129FE17B7A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F343EEC2-F623-44C5-A92F-5F226B1B787E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF64911F-998A-4741-96EF-17736E840084}"/>
 </file>